--- a/backend/data/financials_by_company/1023.HK.xlsx
+++ b/backend/data/financials_by_company/1023.HK.xlsx
@@ -662,574 +662,574 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>90815</v>
+        <v>-215985</v>
       </c>
       <c r="C2" t="n">
-        <v>0.205</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>185143000</v>
+        <v>7458000</v>
       </c>
       <c r="E2" t="n">
-        <v>443000</v>
+        <v>-1309000</v>
       </c>
       <c r="F2" t="n">
-        <v>443000</v>
+        <v>-1309000</v>
       </c>
       <c r="G2" t="n">
-        <v>101888000</v>
+        <v>-79972000</v>
       </c>
       <c r="H2" t="n">
-        <v>55342000</v>
+        <v>82801000</v>
       </c>
       <c r="I2" t="n">
-        <v>1034206000</v>
+        <v>986671000</v>
       </c>
       <c r="J2" t="n">
-        <v>185586000</v>
+        <v>6149000</v>
       </c>
       <c r="K2" t="n">
-        <v>130244000</v>
+        <v>-76652000</v>
       </c>
       <c r="L2" t="n">
-        <v>8341000</v>
+        <v>1631000</v>
       </c>
       <c r="M2" t="n">
-        <v>2079000</v>
+        <v>5519000</v>
       </c>
       <c r="N2" t="n">
-        <v>10420000</v>
+        <v>7150000</v>
       </c>
       <c r="O2" t="n">
-        <v>101535815</v>
+        <v>-78878985</v>
       </c>
       <c r="P2" t="n">
-        <v>101888000</v>
+        <v>-150249000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1476250000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>15534000</v>
-      </c>
+        <v>1324628000</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>974995000</v>
+        <v>962517163</v>
       </c>
       <c r="T2" t="n">
-        <v>963383000</v>
+        <v>962517163</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1045</v>
+        <v>-0.1561</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1058</v>
+        <v>-0.1561</v>
       </c>
       <c r="W2" t="n">
-        <v>101888000</v>
+        <v>-150249000</v>
       </c>
       <c r="X2" t="n">
-        <v>101888000</v>
+        <v>-150249000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>101888000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>-150249000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>3410000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>101888000</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>-153659000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-70277000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>101888000</v>
+        <v>-83382000</v>
       </c>
       <c r="AE2" t="n">
-        <v>26277000</v>
+        <v>1211000</v>
       </c>
       <c r="AF2" t="n">
-        <v>128165000</v>
+        <v>-82171000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-1450000</v>
+        <v>-72281000</v>
       </c>
       <c r="AH2" t="n">
-        <v>443000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-3346000</v>
-      </c>
+        <v>-1309000</v>
+      </c>
+      <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>-443000</v>
+        <v>1309000</v>
       </c>
       <c r="AK2" t="n">
-        <v>8341000</v>
+        <v>1631000</v>
       </c>
       <c r="AL2" t="n">
-        <v>2079000</v>
+        <v>5519000</v>
       </c>
       <c r="AM2" t="n">
-        <v>10420000</v>
+        <v>7150000</v>
       </c>
       <c r="AN2" t="n">
-        <v>130231000</v>
+        <v>-10212000</v>
       </c>
       <c r="AO2" t="n">
-        <v>442044000</v>
+        <v>337957000</v>
       </c>
       <c r="AP2" t="n">
-        <v>444853000</v>
+        <v>354012000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>212269000</v>
+        <v>144044000</v>
       </c>
       <c r="AR2" t="n">
-        <v>232584000</v>
+        <v>209968000</v>
       </c>
       <c r="AS2" t="n">
-        <v>572275000</v>
+        <v>327745000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1034206000</v>
+        <v>986671000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1606481000</v>
+        <v>1314416000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1606481000</v>
+        <v>1314416000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-20952</v>
+        <v>-1134896.234332</v>
       </c>
       <c r="C3" t="n">
-        <v>0.216</v>
+        <v>0.185744</v>
       </c>
       <c r="D3" t="n">
-        <v>323993000</v>
+        <v>269270000</v>
       </c>
       <c r="E3" t="n">
-        <v>-97000</v>
+        <v>-6110000</v>
       </c>
       <c r="F3" t="n">
-        <v>-97000</v>
+        <v>-6110000</v>
       </c>
       <c r="G3" t="n">
-        <v>202796000</v>
+        <v>150506000</v>
       </c>
       <c r="H3" t="n">
-        <v>62183000</v>
+        <v>72926000</v>
       </c>
       <c r="I3" t="n">
-        <v>1222076000</v>
+        <v>1311900000</v>
       </c>
       <c r="J3" t="n">
-        <v>323896000</v>
+        <v>263160000</v>
       </c>
       <c r="K3" t="n">
-        <v>261713000</v>
+        <v>190234000</v>
       </c>
       <c r="L3" t="n">
-        <v>4798000</v>
+        <v>1614000</v>
       </c>
       <c r="M3" t="n">
-        <v>3058000</v>
+        <v>5539000</v>
       </c>
       <c r="N3" t="n">
-        <v>7856000</v>
+        <v>7153000</v>
       </c>
       <c r="O3" t="n">
-        <v>202872048</v>
+        <v>155481103.765668</v>
       </c>
       <c r="P3" t="n">
-        <v>202796000</v>
+        <v>111647000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1605792000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>14669000</v>
-      </c>
+        <v>1678706000</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>963539000</v>
+        <v>965430000</v>
       </c>
       <c r="T3" t="n">
-        <v>963539000</v>
+        <v>962702000</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2105</v>
+        <v>0.1156</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2105</v>
+        <v>0.116</v>
       </c>
       <c r="W3" t="n">
-        <v>202796000</v>
+        <v>111647000</v>
       </c>
       <c r="X3" t="n">
-        <v>202796000</v>
+        <v>111647000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>202796000</v>
+        <v>111647000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>117000</v>
       </c>
       <c r="AB3" t="n">
-        <v>202796000</v>
+        <v>111530000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>-38859000</v>
       </c>
       <c r="AD3" t="n">
-        <v>202796000</v>
+        <v>150389000</v>
       </c>
       <c r="AE3" t="n">
-        <v>55859000</v>
+        <v>34306000</v>
       </c>
       <c r="AF3" t="n">
-        <v>258655000</v>
+        <v>184695000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-8448000</v>
+        <v>6426000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-97000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-2548000</v>
-      </c>
+        <v>-6110000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>97000</v>
+        <v>6110000</v>
       </c>
       <c r="AK3" t="n">
-        <v>4798000</v>
+        <v>1614000</v>
       </c>
       <c r="AL3" t="n">
-        <v>3058000</v>
+        <v>5539000</v>
       </c>
       <c r="AM3" t="n">
-        <v>7856000</v>
+        <v>7153000</v>
       </c>
       <c r="AN3" t="n">
-        <v>222000000</v>
+        <v>167169000</v>
       </c>
       <c r="AO3" t="n">
-        <v>383716000</v>
+        <v>366806000</v>
       </c>
       <c r="AP3" t="n">
-        <v>388725000</v>
+        <v>373769000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>182305000</v>
+        <v>157243000</v>
       </c>
       <c r="AR3" t="n">
-        <v>206420000</v>
+        <v>216526000</v>
       </c>
       <c r="AS3" t="n">
-        <v>605716000</v>
+        <v>533975000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1222076000</v>
+        <v>1311900000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1827792000</v>
+        <v>1845875000</v>
       </c>
       <c r="AV3" t="n">
-        <v>1827792000</v>
+        <v>1845875000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-1134896.234332</v>
+        <v>-20952</v>
       </c>
       <c r="C4" t="n">
-        <v>0.185744</v>
+        <v>0.216</v>
       </c>
       <c r="D4" t="n">
-        <v>269270000</v>
+        <v>323993000</v>
       </c>
       <c r="E4" t="n">
-        <v>-6110000</v>
+        <v>-97000</v>
       </c>
       <c r="F4" t="n">
-        <v>-6110000</v>
+        <v>-97000</v>
       </c>
       <c r="G4" t="n">
-        <v>150506000</v>
+        <v>202796000</v>
       </c>
       <c r="H4" t="n">
-        <v>72926000</v>
+        <v>62183000</v>
       </c>
       <c r="I4" t="n">
-        <v>1311900000</v>
+        <v>1222076000</v>
       </c>
       <c r="J4" t="n">
-        <v>263160000</v>
+        <v>323896000</v>
       </c>
       <c r="K4" t="n">
-        <v>190234000</v>
+        <v>261713000</v>
       </c>
       <c r="L4" t="n">
-        <v>1614000</v>
+        <v>4798000</v>
       </c>
       <c r="M4" t="n">
-        <v>5539000</v>
+        <v>3058000</v>
       </c>
       <c r="N4" t="n">
-        <v>7153000</v>
+        <v>7856000</v>
       </c>
       <c r="O4" t="n">
-        <v>155481103.765668</v>
+        <v>202872048</v>
       </c>
       <c r="P4" t="n">
-        <v>111647000</v>
+        <v>202796000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1678706000</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
+        <v>1605792000</v>
+      </c>
+      <c r="R4" t="n">
+        <v>14669000</v>
+      </c>
       <c r="S4" t="n">
-        <v>965430000</v>
+        <v>963539000</v>
       </c>
       <c r="T4" t="n">
-        <v>962702000</v>
+        <v>963539000</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1156</v>
+        <v>0.2105</v>
       </c>
       <c r="V4" t="n">
-        <v>0.116</v>
+        <v>0.2105</v>
       </c>
       <c r="W4" t="n">
-        <v>111647000</v>
+        <v>202796000</v>
       </c>
       <c r="X4" t="n">
-        <v>111647000</v>
+        <v>202796000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>111647000</v>
+        <v>202796000</v>
       </c>
       <c r="AA4" t="n">
-        <v>117000</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>111530000</v>
+        <v>202796000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-38859000</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>150389000</v>
+        <v>202796000</v>
       </c>
       <c r="AE4" t="n">
-        <v>34306000</v>
+        <v>55859000</v>
       </c>
       <c r="AF4" t="n">
-        <v>184695000</v>
+        <v>258655000</v>
       </c>
       <c r="AG4" t="n">
-        <v>6426000</v>
+        <v>-8448000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-6110000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>-97000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-2548000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>6110000</v>
+        <v>97000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1614000</v>
+        <v>4798000</v>
       </c>
       <c r="AL4" t="n">
-        <v>5539000</v>
+        <v>3058000</v>
       </c>
       <c r="AM4" t="n">
-        <v>7153000</v>
+        <v>7856000</v>
       </c>
       <c r="AN4" t="n">
-        <v>167169000</v>
+        <v>222000000</v>
       </c>
       <c r="AO4" t="n">
-        <v>366806000</v>
+        <v>383716000</v>
       </c>
       <c r="AP4" t="n">
-        <v>373769000</v>
+        <v>388725000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>157243000</v>
+        <v>182305000</v>
       </c>
       <c r="AR4" t="n">
-        <v>216526000</v>
+        <v>206420000</v>
       </c>
       <c r="AS4" t="n">
-        <v>533975000</v>
+        <v>605716000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1311900000</v>
+        <v>1222076000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1845875000</v>
+        <v>1827792000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1845875000</v>
+        <v>1827792000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-215985</v>
+        <v>90815</v>
       </c>
       <c r="C5" t="n">
-        <v>0.165</v>
+        <v>0.205</v>
       </c>
       <c r="D5" t="n">
-        <v>7458000</v>
+        <v>185143000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1309000</v>
+        <v>443000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1309000</v>
+        <v>443000</v>
       </c>
       <c r="G5" t="n">
-        <v>-79972000</v>
+        <v>101888000</v>
       </c>
       <c r="H5" t="n">
-        <v>82801000</v>
+        <v>55342000</v>
       </c>
       <c r="I5" t="n">
-        <v>986671000</v>
+        <v>1034206000</v>
       </c>
       <c r="J5" t="n">
-        <v>6149000</v>
+        <v>185586000</v>
       </c>
       <c r="K5" t="n">
-        <v>-76652000</v>
+        <v>130244000</v>
       </c>
       <c r="L5" t="n">
-        <v>1631000</v>
+        <v>8341000</v>
       </c>
       <c r="M5" t="n">
-        <v>5519000</v>
+        <v>2079000</v>
       </c>
       <c r="N5" t="n">
-        <v>7150000</v>
+        <v>10420000</v>
       </c>
       <c r="O5" t="n">
-        <v>-78878985</v>
+        <v>101535815</v>
       </c>
       <c r="P5" t="n">
-        <v>-150249000</v>
+        <v>101888000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1324628000</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>1476250000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>15534000</v>
+      </c>
       <c r="S5" t="n">
-        <v>962517163</v>
+        <v>974995000</v>
       </c>
       <c r="T5" t="n">
-        <v>962517163</v>
+        <v>963383000</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1561</v>
+        <v>0.1045</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1561</v>
+        <v>0.1058</v>
       </c>
       <c r="W5" t="n">
-        <v>-150249000</v>
+        <v>101888000</v>
       </c>
       <c r="X5" t="n">
-        <v>-150249000</v>
+        <v>101888000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-150249000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>3410000</v>
-      </c>
+        <v>101888000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>-153659000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>-70277000</v>
-      </c>
+        <v>101888000</v>
+      </c>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-83382000</v>
+        <v>101888000</v>
       </c>
       <c r="AE5" t="n">
-        <v>1211000</v>
+        <v>26277000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-82171000</v>
+        <v>128165000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-72281000</v>
+        <v>-1450000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-1309000</v>
-      </c>
-      <c r="AI5" t="inlineStr"/>
+        <v>443000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>-3346000</v>
+      </c>
       <c r="AJ5" t="n">
-        <v>1309000</v>
+        <v>-443000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1631000</v>
+        <v>8341000</v>
       </c>
       <c r="AL5" t="n">
-        <v>5519000</v>
+        <v>2079000</v>
       </c>
       <c r="AM5" t="n">
-        <v>7150000</v>
+        <v>10420000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-10212000</v>
+        <v>130231000</v>
       </c>
       <c r="AO5" t="n">
-        <v>337957000</v>
+        <v>442044000</v>
       </c>
       <c r="AP5" t="n">
-        <v>354012000</v>
+        <v>444853000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>144044000</v>
+        <v>212269000</v>
       </c>
       <c r="AR5" t="n">
-        <v>209968000</v>
+        <v>232584000</v>
       </c>
       <c r="AS5" t="n">
-        <v>327745000</v>
+        <v>572275000</v>
       </c>
       <c r="AT5" t="n">
-        <v>986671000</v>
+        <v>1034206000</v>
       </c>
       <c r="AU5" t="n">
-        <v>1314416000</v>
+        <v>1606481000</v>
       </c>
       <c r="AV5" t="n">
-        <v>1314416000</v>
+        <v>1606481000</v>
       </c>
     </row>
   </sheetData>
@@ -1600,62 +1600,64 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>6430000</v>
+        <v>2728000</v>
       </c>
       <c r="C2" t="n">
-        <v>959000000</v>
+        <v>959974000</v>
       </c>
       <c r="D2" t="n">
-        <v>965430000</v>
+        <v>962702000</v>
       </c>
       <c r="E2" t="n">
-        <v>35767000</v>
+        <v>210785000</v>
       </c>
       <c r="F2" t="n">
-        <v>1789627000</v>
+        <v>1718020000</v>
       </c>
       <c r="G2" t="n">
-        <v>1805399000</v>
+        <v>1868547000</v>
       </c>
       <c r="H2" t="n">
-        <v>769686000</v>
+        <v>587054000</v>
       </c>
       <c r="I2" t="n">
-        <v>1789627000</v>
+        <v>1718020000</v>
       </c>
       <c r="J2" t="n">
-        <v>35767000</v>
+        <v>84186000</v>
       </c>
       <c r="K2" t="n">
-        <v>1805399000</v>
+        <v>1741948000</v>
       </c>
       <c r="L2" t="n">
-        <v>1805399000</v>
+        <v>1741948000</v>
       </c>
       <c r="M2" t="n">
-        <v>1805399000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>1748735000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>6787000</v>
+      </c>
       <c r="O2" t="n">
-        <v>1805399000</v>
+        <v>1741948000</v>
       </c>
       <c r="P2" t="n">
-        <v>12389000</v>
+        <v>11137000</v>
       </c>
       <c r="Q2" t="n">
         <v>24688000</v>
       </c>
       <c r="R2" t="n">
-        <v>4044000</v>
+        <v>6375000</v>
       </c>
       <c r="S2" t="n">
-        <v>865199000</v>
+        <v>679449000</v>
       </c>
       <c r="T2" t="n">
-        <v>924811000</v>
+        <v>922063000</v>
       </c>
       <c r="U2" t="n">
         <v>96543000</v>
@@ -1664,199 +1666,213 @@
         <v>96543000</v>
       </c>
       <c r="W2" t="n">
-        <v>308737000</v>
+        <v>569542000</v>
       </c>
       <c r="X2" t="n">
-        <v>24431000</v>
+        <v>52575000</v>
       </c>
       <c r="Y2" t="n">
-        <v>337000</v>
+        <v>2486000</v>
       </c>
       <c r="Z2" t="n">
-        <v>5551000</v>
+        <v>7526000</v>
       </c>
       <c r="AA2" t="n">
-        <v>18543000</v>
+        <v>42563000</v>
       </c>
       <c r="AB2" t="n">
-        <v>18543000</v>
+        <v>42563000</v>
       </c>
       <c r="AC2" t="n">
-        <v>284306000</v>
+        <v>516967000</v>
       </c>
       <c r="AD2" t="n">
-        <v>17224000</v>
+        <v>168222000</v>
       </c>
       <c r="AE2" t="n">
-        <v>17224000</v>
-      </c>
-      <c r="AF2" t="inlineStr"/>
+        <v>41623000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>126599000</v>
+      </c>
       <c r="AG2" t="n">
-        <v>256823000</v>
+        <v>332884000</v>
       </c>
       <c r="AH2" t="n">
-        <v>80331000</v>
+        <v>103565000</v>
       </c>
       <c r="AI2" t="n">
-        <v>42938000</v>
+        <v>19065000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>133554000</v>
+        <v>210254000</v>
       </c>
       <c r="AK2" t="n">
-        <v>2114136000</v>
+        <v>2318277000</v>
       </c>
       <c r="AL2" t="n">
-        <v>1060144000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+        <v>1214256000</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>12366000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>10006000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>13718000</v>
-      </c>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
+        <v>38939000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9644000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9644000</v>
+      </c>
       <c r="AR2" t="n">
-        <v>683056000</v>
+        <v>699956000</v>
       </c>
       <c r="AS2" t="n">
-        <v>15772000</v>
+        <v>23928000</v>
       </c>
       <c r="AT2" t="n">
-        <v>15772000</v>
+        <v>23928000</v>
       </c>
       <c r="AU2" t="n">
-        <v>347598000</v>
+        <v>431783000</v>
       </c>
       <c r="AV2" t="n">
-        <v>-399194000</v>
+        <v>-512761000</v>
       </c>
       <c r="AW2" t="n">
-        <v>746792000</v>
+        <v>944544000</v>
       </c>
       <c r="AX2" t="n">
-        <v>25622000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>4328000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>445375000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>178824000</v>
+        <v>319116000</v>
       </c>
       <c r="BA2" t="n">
-        <v>542346000</v>
+        <v>621100000</v>
       </c>
       <c r="BB2" t="n">
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>1053992000</v>
+        <v>1104021000</v>
       </c>
       <c r="BD2" t="n">
-        <v>25939000</v>
+        <v>25219000</v>
       </c>
       <c r="BE2" t="n">
-        <v>10492000</v>
+        <v>14471000</v>
       </c>
       <c r="BF2" t="n">
-        <v>217220000</v>
+        <v>285823000</v>
       </c>
       <c r="BG2" t="n">
-        <v>-6723000</v>
+        <v>-95370000</v>
       </c>
       <c r="BH2" t="n">
-        <v>120521000</v>
+        <v>202990000</v>
       </c>
       <c r="BI2" t="n">
-        <v>78852000</v>
+        <v>96181000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>24570000</v>
+        <v>82022000</v>
       </c>
       <c r="BK2" t="n">
-        <v>19504000</v>
+        <v>29144000</v>
       </c>
       <c r="BL2" t="n">
-        <v>23101000</v>
+        <v>41752000</v>
       </c>
       <c r="BM2" t="n">
-        <v>297185000</v>
+        <v>229792000</v>
       </c>
       <c r="BN2" t="n">
-        <v>-3496000</v>
+        <v>-3718000</v>
       </c>
       <c r="BO2" t="n">
-        <v>300681000</v>
+        <v>233510000</v>
       </c>
       <c r="BP2" t="n">
-        <v>460551000</v>
+        <v>477820000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>460551000</v>
-      </c>
-      <c r="BR2" t="inlineStr"/>
+        <v>477820000</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>2922000</v>
+      </c>
       <c r="BS2" t="n">
-        <v>460551000</v>
+        <v>474898000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>2728000</v>
       </c>
       <c r="C3" t="n">
-        <v>965430000</v>
+        <v>959974000</v>
       </c>
       <c r="D3" t="n">
-        <v>965430000</v>
+        <v>962702000</v>
       </c>
       <c r="E3" t="n">
-        <v>47510000</v>
+        <v>108596000</v>
       </c>
       <c r="F3" t="n">
-        <v>1763716000</v>
+        <v>1748131000</v>
       </c>
       <c r="G3" t="n">
-        <v>1779748000</v>
+        <v>1828195000</v>
       </c>
       <c r="H3" t="n">
-        <v>758992000</v>
+        <v>694642000</v>
       </c>
       <c r="I3" t="n">
-        <v>1763716000</v>
+        <v>1748131000</v>
       </c>
       <c r="J3" t="n">
-        <v>47510000</v>
+        <v>46052000</v>
       </c>
       <c r="K3" t="n">
-        <v>1779748000</v>
+        <v>1765651000</v>
       </c>
       <c r="L3" t="n">
-        <v>1779748000</v>
+        <v>1765651000</v>
       </c>
       <c r="M3" t="n">
-        <v>1779748000</v>
+        <v>1765651000</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1779748000</v>
+        <v>1765651000</v>
       </c>
       <c r="P3" t="n">
-        <v>4838000</v>
+        <v>11137000</v>
       </c>
       <c r="Q3" t="n">
         <v>24688000</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>6375000</v>
       </c>
       <c r="S3" t="n">
-        <v>855794000</v>
+        <v>753380000</v>
       </c>
       <c r="T3" t="n">
-        <v>924811000</v>
+        <v>922063000</v>
       </c>
       <c r="U3" t="n">
         <v>96543000</v>
@@ -1865,205 +1881,211 @@
         <v>96543000</v>
       </c>
       <c r="W3" t="n">
-        <v>358991000</v>
+        <v>450530000</v>
       </c>
       <c r="X3" t="n">
-        <v>30328000</v>
+        <v>31244000</v>
       </c>
       <c r="Y3" t="n">
-        <v>1111000</v>
+        <v>1923000</v>
       </c>
       <c r="Z3" t="n">
-        <v>5160000</v>
+        <v>7135000</v>
       </c>
       <c r="AA3" t="n">
-        <v>24057000</v>
+        <v>22186000</v>
       </c>
       <c r="AB3" t="n">
-        <v>24057000</v>
+        <v>22186000</v>
       </c>
       <c r="AC3" t="n">
-        <v>328663000</v>
+        <v>419286000</v>
       </c>
       <c r="AD3" t="n">
-        <v>23453000</v>
+        <v>86410000</v>
       </c>
       <c r="AE3" t="n">
-        <v>23453000</v>
+        <v>23866000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>62544000</v>
       </c>
       <c r="AG3" t="n">
-        <v>290498000</v>
+        <v>314977000</v>
       </c>
       <c r="AH3" t="n">
-        <v>76845000</v>
+        <v>78383000</v>
       </c>
       <c r="AI3" t="n">
-        <v>51992000</v>
+        <v>11338000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>161661000</v>
+        <v>225256000</v>
       </c>
       <c r="AK3" t="n">
-        <v>2138739000</v>
+        <v>2216181000</v>
       </c>
       <c r="AL3" t="n">
-        <v>1051084000</v>
+        <v>1102253000</v>
       </c>
       <c r="AM3" t="n">
-        <v>163000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>554000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
       <c r="AO3" t="n">
-        <v>15315000</v>
-      </c>
-      <c r="AP3" t="inlineStr"/>
+        <v>20950000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>692456000</v>
+        <v>699756000</v>
       </c>
       <c r="AS3" t="n">
-        <v>16032000</v>
+        <v>17520000</v>
       </c>
       <c r="AT3" t="n">
-        <v>16032000</v>
+        <v>17520000</v>
       </c>
       <c r="AU3" t="n">
-        <v>327281000</v>
+        <v>364027000</v>
       </c>
       <c r="AV3" t="n">
-        <v>-393561000</v>
+        <v>-425736000</v>
       </c>
       <c r="AW3" t="n">
-        <v>720842000</v>
+        <v>789763000</v>
       </c>
       <c r="AX3" t="n">
-        <v>4075000</v>
+        <v>2469000</v>
       </c>
       <c r="AY3" t="n">
-        <v>340726000</v>
+        <v>378569000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>200717000</v>
+        <v>242862000</v>
       </c>
       <c r="BA3" t="n">
-        <v>516050000</v>
+        <v>544432000</v>
       </c>
       <c r="BB3" t="n">
         <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>1087655000</v>
+        <v>1113928000</v>
       </c>
       <c r="BD3" t="n">
-        <v>24793000</v>
+        <v>46858000</v>
       </c>
       <c r="BE3" t="n">
-        <v>8911000</v>
+        <v>8567000</v>
       </c>
       <c r="BF3" t="n">
-        <v>214441000</v>
+        <v>286719000</v>
       </c>
       <c r="BG3" t="n">
-        <v>-10786000</v>
+        <v>-26674000</v>
       </c>
       <c r="BH3" t="n">
-        <v>118690000</v>
+        <v>155482000</v>
       </c>
       <c r="BI3" t="n">
-        <v>72350000</v>
+        <v>96596000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>34187000</v>
+        <v>61315000</v>
       </c>
       <c r="BK3" t="n">
-        <v>61051000</v>
+        <v>27324000</v>
       </c>
       <c r="BL3" t="n">
-        <v>1684000</v>
+        <v>46803000</v>
       </c>
       <c r="BM3" t="n">
-        <v>381831000</v>
+        <v>382874000</v>
       </c>
       <c r="BN3" t="n">
-        <v>-4976000</v>
+        <v>-6457000</v>
       </c>
       <c r="BO3" t="n">
-        <v>386807000</v>
+        <v>389331000</v>
       </c>
       <c r="BP3" t="n">
-        <v>403855000</v>
+        <v>314783000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>403855000</v>
-      </c>
-      <c r="BR3" t="inlineStr"/>
+        <v>314783000</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>0</v>
+      </c>
       <c r="BS3" t="n">
-        <v>403855000</v>
+        <v>314783000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>2728000</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>959974000</v>
+        <v>965430000</v>
       </c>
       <c r="D4" t="n">
-        <v>962702000</v>
+        <v>965430000</v>
       </c>
       <c r="E4" t="n">
-        <v>108596000</v>
+        <v>47510000</v>
       </c>
       <c r="F4" t="n">
-        <v>1748131000</v>
+        <v>1763716000</v>
       </c>
       <c r="G4" t="n">
-        <v>1828195000</v>
+        <v>1779748000</v>
       </c>
       <c r="H4" t="n">
-        <v>694642000</v>
+        <v>758992000</v>
       </c>
       <c r="I4" t="n">
-        <v>1748131000</v>
+        <v>1763716000</v>
       </c>
       <c r="J4" t="n">
-        <v>46052000</v>
+        <v>47510000</v>
       </c>
       <c r="K4" t="n">
-        <v>1765651000</v>
+        <v>1779748000</v>
       </c>
       <c r="L4" t="n">
-        <v>1765651000</v>
+        <v>1779748000</v>
       </c>
       <c r="M4" t="n">
-        <v>1765651000</v>
+        <v>1779748000</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1765651000</v>
+        <v>1779748000</v>
       </c>
       <c r="P4" t="n">
-        <v>11137000</v>
+        <v>4838000</v>
       </c>
       <c r="Q4" t="n">
         <v>24688000</v>
       </c>
       <c r="R4" t="n">
-        <v>6375000</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>753380000</v>
+        <v>855794000</v>
       </c>
       <c r="T4" t="n">
-        <v>922063000</v>
+        <v>924811000</v>
       </c>
       <c r="U4" t="n">
         <v>96543000</v>
@@ -2072,211 +2094,203 @@
         <v>96543000</v>
       </c>
       <c r="W4" t="n">
-        <v>450530000</v>
+        <v>358991000</v>
       </c>
       <c r="X4" t="n">
-        <v>31244000</v>
+        <v>30328000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1923000</v>
+        <v>1111000</v>
       </c>
       <c r="Z4" t="n">
-        <v>7135000</v>
+        <v>5160000</v>
       </c>
       <c r="AA4" t="n">
-        <v>22186000</v>
+        <v>24057000</v>
       </c>
       <c r="AB4" t="n">
-        <v>22186000</v>
+        <v>24057000</v>
       </c>
       <c r="AC4" t="n">
-        <v>419286000</v>
+        <v>328663000</v>
       </c>
       <c r="AD4" t="n">
-        <v>86410000</v>
+        <v>23453000</v>
       </c>
       <c r="AE4" t="n">
-        <v>23866000</v>
+        <v>23453000</v>
       </c>
       <c r="AF4" t="n">
-        <v>62544000</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>314977000</v>
+        <v>290498000</v>
       </c>
       <c r="AH4" t="n">
-        <v>78383000</v>
+        <v>76845000</v>
       </c>
       <c r="AI4" t="n">
-        <v>11338000</v>
+        <v>51992000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>225256000</v>
+        <v>161661000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2216181000</v>
+        <v>2138739000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1102253000</v>
+        <v>1051084000</v>
       </c>
       <c r="AM4" t="n">
-        <v>554000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
+        <v>163000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>20950000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+        <v>15315000</v>
+      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>699756000</v>
+        <v>692456000</v>
       </c>
       <c r="AS4" t="n">
-        <v>17520000</v>
+        <v>16032000</v>
       </c>
       <c r="AT4" t="n">
-        <v>17520000</v>
+        <v>16032000</v>
       </c>
       <c r="AU4" t="n">
-        <v>364027000</v>
+        <v>327281000</v>
       </c>
       <c r="AV4" t="n">
-        <v>-425736000</v>
+        <v>-393561000</v>
       </c>
       <c r="AW4" t="n">
-        <v>789763000</v>
+        <v>720842000</v>
       </c>
       <c r="AX4" t="n">
-        <v>2469000</v>
+        <v>4075000</v>
       </c>
       <c r="AY4" t="n">
-        <v>378569000</v>
+        <v>340726000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>242862000</v>
+        <v>200717000</v>
       </c>
       <c r="BA4" t="n">
-        <v>544432000</v>
+        <v>516050000</v>
       </c>
       <c r="BB4" t="n">
         <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>1113928000</v>
+        <v>1087655000</v>
       </c>
       <c r="BD4" t="n">
-        <v>46858000</v>
+        <v>24793000</v>
       </c>
       <c r="BE4" t="n">
-        <v>8567000</v>
+        <v>8911000</v>
       </c>
       <c r="BF4" t="n">
-        <v>286719000</v>
+        <v>214441000</v>
       </c>
       <c r="BG4" t="n">
-        <v>-26674000</v>
+        <v>-10786000</v>
       </c>
       <c r="BH4" t="n">
-        <v>155482000</v>
+        <v>118690000</v>
       </c>
       <c r="BI4" t="n">
-        <v>96596000</v>
+        <v>72350000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>61315000</v>
+        <v>34187000</v>
       </c>
       <c r="BK4" t="n">
-        <v>27324000</v>
+        <v>61051000</v>
       </c>
       <c r="BL4" t="n">
-        <v>46803000</v>
+        <v>1684000</v>
       </c>
       <c r="BM4" t="n">
-        <v>382874000</v>
+        <v>381831000</v>
       </c>
       <c r="BN4" t="n">
-        <v>-6457000</v>
+        <v>-4976000</v>
       </c>
       <c r="BO4" t="n">
-        <v>389331000</v>
+        <v>386807000</v>
       </c>
       <c r="BP4" t="n">
-        <v>314783000</v>
+        <v>403855000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>314783000</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>0</v>
-      </c>
+        <v>403855000</v>
+      </c>
+      <c r="BR4" t="inlineStr"/>
       <c r="BS4" t="n">
-        <v>314783000</v>
+        <v>403855000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>2728000</v>
+        <v>6430000</v>
       </c>
       <c r="C5" t="n">
-        <v>959974000</v>
+        <v>959000000</v>
       </c>
       <c r="D5" t="n">
-        <v>962702000</v>
+        <v>965430000</v>
       </c>
       <c r="E5" t="n">
-        <v>210785000</v>
+        <v>35767000</v>
       </c>
       <c r="F5" t="n">
-        <v>1718020000</v>
+        <v>1789627000</v>
       </c>
       <c r="G5" t="n">
-        <v>1868547000</v>
+        <v>1805399000</v>
       </c>
       <c r="H5" t="n">
-        <v>587054000</v>
+        <v>769686000</v>
       </c>
       <c r="I5" t="n">
-        <v>1718020000</v>
+        <v>1789627000</v>
       </c>
       <c r="J5" t="n">
-        <v>84186000</v>
+        <v>35767000</v>
       </c>
       <c r="K5" t="n">
-        <v>1741948000</v>
+        <v>1805399000</v>
       </c>
       <c r="L5" t="n">
-        <v>1741948000</v>
+        <v>1805399000</v>
       </c>
       <c r="M5" t="n">
-        <v>1748735000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6787000</v>
-      </c>
+        <v>1805399000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>1741948000</v>
+        <v>1805399000</v>
       </c>
       <c r="P5" t="n">
-        <v>11137000</v>
+        <v>12389000</v>
       </c>
       <c r="Q5" t="n">
         <v>24688000</v>
       </c>
       <c r="R5" t="n">
-        <v>6375000</v>
+        <v>4044000</v>
       </c>
       <c r="S5" t="n">
-        <v>679449000</v>
+        <v>865199000</v>
       </c>
       <c r="T5" t="n">
-        <v>922063000</v>
+        <v>924811000</v>
       </c>
       <c r="U5" t="n">
         <v>96543000</v>
@@ -2285,151 +2299,137 @@
         <v>96543000</v>
       </c>
       <c r="W5" t="n">
-        <v>569542000</v>
+        <v>308737000</v>
       </c>
       <c r="X5" t="n">
-        <v>52575000</v>
+        <v>24431000</v>
       </c>
       <c r="Y5" t="n">
-        <v>2486000</v>
+        <v>337000</v>
       </c>
       <c r="Z5" t="n">
-        <v>7526000</v>
+        <v>5551000</v>
       </c>
       <c r="AA5" t="n">
-        <v>42563000</v>
+        <v>18543000</v>
       </c>
       <c r="AB5" t="n">
-        <v>42563000</v>
+        <v>18543000</v>
       </c>
       <c r="AC5" t="n">
-        <v>516967000</v>
+        <v>284306000</v>
       </c>
       <c r="AD5" t="n">
-        <v>168222000</v>
+        <v>17224000</v>
       </c>
       <c r="AE5" t="n">
-        <v>41623000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>126599000</v>
-      </c>
+        <v>17224000</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>332884000</v>
+        <v>256823000</v>
       </c>
       <c r="AH5" t="n">
-        <v>103565000</v>
+        <v>80331000</v>
       </c>
       <c r="AI5" t="n">
-        <v>19065000</v>
+        <v>42938000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>210254000</v>
+        <v>133554000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2318277000</v>
+        <v>2114136000</v>
       </c>
       <c r="AL5" t="n">
-        <v>1214256000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>12366000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>10006000</v>
-      </c>
+        <v>1060144000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>38939000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9644000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>9644000</v>
-      </c>
+        <v>13718000</v>
+      </c>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
-        <v>699956000</v>
+        <v>683056000</v>
       </c>
       <c r="AS5" t="n">
-        <v>23928000</v>
+        <v>15772000</v>
       </c>
       <c r="AT5" t="n">
-        <v>23928000</v>
+        <v>15772000</v>
       </c>
       <c r="AU5" t="n">
-        <v>431783000</v>
+        <v>347598000</v>
       </c>
       <c r="AV5" t="n">
-        <v>-512761000</v>
+        <v>-399194000</v>
       </c>
       <c r="AW5" t="n">
-        <v>944544000</v>
+        <v>746792000</v>
       </c>
       <c r="AX5" t="n">
-        <v>4328000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>445375000</v>
-      </c>
+        <v>25622000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>319116000</v>
+        <v>178824000</v>
       </c>
       <c r="BA5" t="n">
-        <v>621100000</v>
+        <v>542346000</v>
       </c>
       <c r="BB5" t="n">
         <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>1104021000</v>
+        <v>1053992000</v>
       </c>
       <c r="BD5" t="n">
-        <v>25219000</v>
+        <v>25939000</v>
       </c>
       <c r="BE5" t="n">
-        <v>14471000</v>
+        <v>10492000</v>
       </c>
       <c r="BF5" t="n">
-        <v>285823000</v>
+        <v>217220000</v>
       </c>
       <c r="BG5" t="n">
-        <v>-95370000</v>
+        <v>-6723000</v>
       </c>
       <c r="BH5" t="n">
-        <v>202990000</v>
+        <v>120521000</v>
       </c>
       <c r="BI5" t="n">
-        <v>96181000</v>
+        <v>78852000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>82022000</v>
+        <v>24570000</v>
       </c>
       <c r="BK5" t="n">
-        <v>29144000</v>
+        <v>19504000</v>
       </c>
       <c r="BL5" t="n">
-        <v>41752000</v>
+        <v>23101000</v>
       </c>
       <c r="BM5" t="n">
-        <v>229792000</v>
+        <v>297185000</v>
       </c>
       <c r="BN5" t="n">
-        <v>-3718000</v>
+        <v>-3496000</v>
       </c>
       <c r="BO5" t="n">
-        <v>233510000</v>
+        <v>300681000</v>
       </c>
       <c r="BP5" t="n">
-        <v>477820000</v>
+        <v>460551000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>477820000</v>
-      </c>
-      <c r="BR5" t="n">
-        <v>2922000</v>
-      </c>
+        <v>460551000</v>
+      </c>
+      <c r="BR5" t="inlineStr"/>
       <c r="BS5" t="n">
-        <v>474898000</v>
+        <v>460551000</v>
       </c>
     </row>
   </sheetData>
@@ -2705,576 +2705,576 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>173744000</v>
+        <v>99399000</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>-4044000</v>
-      </c>
+        <v>-179877000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>100439000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>-64176000</v>
+        <v>-14113000</v>
       </c>
       <c r="G2" t="n">
-        <v>460551000</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>477820000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2922000</v>
+      </c>
       <c r="I2" t="n">
-        <v>403855000</v>
+        <v>517822000</v>
       </c>
       <c r="J2" t="n">
-        <v>2815000</v>
+        <v>36164000</v>
       </c>
       <c r="K2" t="n">
-        <v>53881000</v>
+        <v>-79088000</v>
       </c>
       <c r="L2" t="n">
-        <v>-120420000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-1001000</v>
-      </c>
+        <v>-178548000</v>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>-2079000</v>
+        <v>-8742000</v>
       </c>
       <c r="O2" t="n">
-        <v>-86816000</v>
+        <v>-48135000</v>
       </c>
       <c r="P2" t="n">
-        <v>-86816000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-4044000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-4044000</v>
-      </c>
+        <v>-48135000</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-79438000</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-179877000</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-179877000</v>
       </c>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="W2" t="n">
+        <v>-79438000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-179877000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>100439000</v>
+      </c>
       <c r="Z2" t="n">
-        <v>-63619000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+        <v>-14052000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>368000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>368000</v>
+      </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>-800000</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
       </c>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
+      <c r="AE2" t="n">
+        <v>-800000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>-224000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>-224000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>-63619000</v>
+        <v>-13396000</v>
       </c>
       <c r="AI2" t="n">
-        <v>557000</v>
+        <v>493000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-64176000</v>
+        <v>-13889000</v>
       </c>
       <c r="AK2" t="n">
-        <v>237920000</v>
+        <v>113512000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-32783000</v>
+        <v>-15908000</v>
       </c>
       <c r="AM2" t="n">
-        <v>69815000</v>
-      </c>
-      <c r="AN2" t="inlineStr"/>
+        <v>208894000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-2922000</v>
+      </c>
       <c r="AO2" t="n">
-        <v>-28869000</v>
+        <v>110806000</v>
       </c>
       <c r="AP2" t="n">
-        <v>9497000</v>
+        <v>5996000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3439000</v>
+        <v>45664000</v>
       </c>
       <c r="AR2" t="n">
-        <v>85748000</v>
+        <v>49350000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1528000</v>
+        <v>4746000</v>
       </c>
       <c r="AT2" t="n">
-        <v>7551000</v>
+        <v>2138000</v>
       </c>
       <c r="AU2" t="n">
-        <v>55342000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
+        <v>82801000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>253000</v>
+      </c>
       <c r="AW2" t="n">
-        <v>55342000</v>
+        <v>82548000</v>
       </c>
       <c r="AX2" t="n">
-        <v>9400000</v>
+        <v>11400000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2419000</v>
+        <v>1279000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>128165000</v>
+        <v>-135266000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>269180000</v>
+        <v>-42957000</v>
       </c>
       <c r="C3" t="n">
-        <v>-62645000</v>
+        <v>-266506000</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
+        <v>204657000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-14665000</v>
+        <v>-12982000</v>
       </c>
       <c r="G3" t="n">
-        <v>403855000</v>
+        <v>314783000</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>314783000</v>
+        <v>477820000</v>
       </c>
       <c r="J3" t="n">
-        <v>-19893000</v>
+        <v>-7884000</v>
       </c>
       <c r="K3" t="n">
-        <v>108965000</v>
+        <v>-155153000</v>
       </c>
       <c r="L3" t="n">
-        <v>-168649000</v>
+        <v>-156790000</v>
       </c>
       <c r="M3" t="n">
-        <v>21215000</v>
+        <v>-21639000</v>
       </c>
       <c r="N3" t="n">
-        <v>-3058000</v>
+        <v>-7289000</v>
       </c>
       <c r="O3" t="n">
-        <v>-96270000</v>
+        <v>-28881000</v>
       </c>
       <c r="P3" t="n">
-        <v>-96270000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
+        <v>-28881000</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-62645000</v>
+        <v>-61849000</v>
       </c>
       <c r="T3" t="n">
-        <v>-62645000</v>
+        <v>-61849000</v>
       </c>
       <c r="U3" t="n">
-        <v>-62645000</v>
+        <v>-266506000</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>204657000</v>
       </c>
       <c r="W3" t="n">
-        <v>-62645000</v>
+        <v>-61849000</v>
       </c>
       <c r="X3" t="n">
-        <v>-62645000</v>
+        <v>-266506000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>204657000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-6231000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
+        <v>31612000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
       <c r="AC3" t="n">
-        <v>6567000</v>
+        <v>42442000</v>
       </c>
       <c r="AD3" t="n">
-        <v>6567000</v>
-      </c>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+        <v>42442000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
       <c r="AH3" t="n">
-        <v>-12798000</v>
+        <v>-10830000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1867000</v>
+        <v>2152000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-14665000</v>
+        <v>-12982000</v>
       </c>
       <c r="AK3" t="n">
-        <v>283845000</v>
+        <v>-29975000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-12766000</v>
+        <v>-22113000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-25039000</v>
-      </c>
-      <c r="AN3" t="inlineStr"/>
+        <v>-222166000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
       <c r="AO3" t="n">
-        <v>-109464000</v>
+        <v>-7095000</v>
       </c>
       <c r="AP3" t="n">
-        <v>19496000</v>
+        <v>1254000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>58561000</v>
+        <v>-48927000</v>
       </c>
       <c r="AR3" t="n">
-        <v>6368000</v>
+        <v>-167398000</v>
       </c>
       <c r="AS3" t="n">
-        <v>580000</v>
+        <v>6178000</v>
       </c>
       <c r="AT3" t="n">
-        <v>2824000</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>62183000</v>
+        <v>72926000</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>253000</v>
       </c>
       <c r="AW3" t="n">
-        <v>62183000</v>
+        <v>72673000</v>
       </c>
       <c r="AX3" t="n">
-        <v>7300000</v>
+        <v>200000</v>
       </c>
       <c r="AY3" t="n">
-        <v>4573000</v>
+        <v>497000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>258655000</v>
+        <v>140338000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-42957000</v>
+        <v>269180000</v>
       </c>
       <c r="C4" t="n">
-        <v>-266506000</v>
+        <v>-62645000</v>
       </c>
       <c r="D4" t="n">
-        <v>204657000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="n">
-        <v>-12982000</v>
+        <v>-14665000</v>
       </c>
       <c r="G4" t="n">
-        <v>314783000</v>
+        <v>403855000</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>477820000</v>
+        <v>314783000</v>
       </c>
       <c r="J4" t="n">
-        <v>-7884000</v>
+        <v>-19893000</v>
       </c>
       <c r="K4" t="n">
-        <v>-155153000</v>
+        <v>108965000</v>
       </c>
       <c r="L4" t="n">
-        <v>-156790000</v>
+        <v>-168649000</v>
       </c>
       <c r="M4" t="n">
-        <v>-21639000</v>
+        <v>21215000</v>
       </c>
       <c r="N4" t="n">
-        <v>-7289000</v>
+        <v>-3058000</v>
       </c>
       <c r="O4" t="n">
-        <v>-28881000</v>
+        <v>-96270000</v>
       </c>
       <c r="P4" t="n">
-        <v>-28881000</v>
-      </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
+        <v>-96270000</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
       <c r="S4" t="n">
-        <v>-61849000</v>
+        <v>-62645000</v>
       </c>
       <c r="T4" t="n">
-        <v>-61849000</v>
+        <v>-62645000</v>
       </c>
       <c r="U4" t="n">
-        <v>-266506000</v>
+        <v>-62645000</v>
       </c>
       <c r="V4" t="n">
-        <v>204657000</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>-61849000</v>
+        <v>-62645000</v>
       </c>
       <c r="X4" t="n">
-        <v>-266506000</v>
+        <v>-62645000</v>
       </c>
       <c r="Y4" t="n">
-        <v>204657000</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>31612000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
+        <v>-6231000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>42442000</v>
+        <v>6567000</v>
       </c>
       <c r="AD4" t="n">
-        <v>42442000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
+        <v>6567000</v>
+      </c>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-10830000</v>
+        <v>-12798000</v>
       </c>
       <c r="AI4" t="n">
-        <v>2152000</v>
+        <v>1867000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-12982000</v>
+        <v>-14665000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-29975000</v>
+        <v>283845000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-22113000</v>
+        <v>-12766000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-222166000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
+        <v>-25039000</v>
+      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
-        <v>-7095000</v>
+        <v>-109464000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1254000</v>
+        <v>19496000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-48927000</v>
+        <v>58561000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-167398000</v>
+        <v>6368000</v>
       </c>
       <c r="AS4" t="n">
-        <v>6178000</v>
+        <v>580000</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>2824000</v>
       </c>
       <c r="AU4" t="n">
-        <v>72926000</v>
+        <v>62183000</v>
       </c>
       <c r="AV4" t="n">
-        <v>253000</v>
+        <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>72673000</v>
+        <v>62183000</v>
       </c>
       <c r="AX4" t="n">
-        <v>200000</v>
+        <v>7300000</v>
       </c>
       <c r="AY4" t="n">
-        <v>497000</v>
+        <v>4573000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>140338000</v>
+        <v>258655000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>99399000</v>
+        <v>173744000</v>
       </c>
       <c r="C5" t="n">
-        <v>-179877000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>100439000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>-4044000</v>
+      </c>
       <c r="F5" t="n">
-        <v>-14113000</v>
+        <v>-64176000</v>
       </c>
       <c r="G5" t="n">
-        <v>477820000</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2922000</v>
-      </c>
+        <v>460551000</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>517822000</v>
+        <v>403855000</v>
       </c>
       <c r="J5" t="n">
-        <v>36164000</v>
+        <v>2815000</v>
       </c>
       <c r="K5" t="n">
-        <v>-79088000</v>
+        <v>53881000</v>
       </c>
       <c r="L5" t="n">
-        <v>-178548000</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
+        <v>-120420000</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-1001000</v>
+      </c>
       <c r="N5" t="n">
-        <v>-8742000</v>
+        <v>-2079000</v>
       </c>
       <c r="O5" t="n">
-        <v>-48135000</v>
+        <v>-86816000</v>
       </c>
       <c r="P5" t="n">
-        <v>-48135000</v>
-      </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
+        <v>-86816000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-4044000</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-4044000</v>
+      </c>
       <c r="S5" t="n">
-        <v>-79438000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-179877000</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-179877000</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="n">
-        <v>-79438000</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-179877000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>100439000</v>
-      </c>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="n">
-        <v>-14052000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>368000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>368000</v>
-      </c>
+        <v>-63619000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>-800000</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
-      <c r="AE5" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>-224000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>-224000</v>
-      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>-13396000</v>
+        <v>-63619000</v>
       </c>
       <c r="AI5" t="n">
-        <v>493000</v>
+        <v>557000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-13889000</v>
+        <v>-64176000</v>
       </c>
       <c r="AK5" t="n">
-        <v>113512000</v>
+        <v>237920000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-15908000</v>
+        <v>-32783000</v>
       </c>
       <c r="AM5" t="n">
-        <v>208894000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>-2922000</v>
-      </c>
+        <v>69815000</v>
+      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
-        <v>110806000</v>
+        <v>-28869000</v>
       </c>
       <c r="AP5" t="n">
-        <v>5996000</v>
+        <v>9497000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>45664000</v>
+        <v>3439000</v>
       </c>
       <c r="AR5" t="n">
-        <v>49350000</v>
+        <v>85748000</v>
       </c>
       <c r="AS5" t="n">
-        <v>4746000</v>
+        <v>1528000</v>
       </c>
       <c r="AT5" t="n">
-        <v>2138000</v>
+        <v>7551000</v>
       </c>
       <c r="AU5" t="n">
-        <v>82801000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>253000</v>
-      </c>
+        <v>55342000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>82548000</v>
+        <v>55342000</v>
       </c>
       <c r="AX5" t="n">
-        <v>11400000</v>
+        <v>9400000</v>
       </c>
       <c r="AY5" t="n">
-        <v>1279000</v>
+        <v>2419000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-135266000</v>
+        <v>128165000</v>
       </c>
     </row>
   </sheetData>
@@ -3824,182 +3824,182 @@
       </c>
       <c r="DC1" t="inlineStr">
         <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
       <c r="EM1" t="inlineStr">
@@ -4102,34 +4102,34 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.48</v>
+        <v>0.475</v>
       </c>
       <c r="V2" t="n">
-        <v>0.48</v>
+        <v>0.475</v>
       </c>
       <c r="W2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="X2" t="n">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.48</v>
+        <v>0.475</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.48</v>
+        <v>0.475</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.485</v>
+        <v>0.475</v>
       </c>
       <c r="AC2" t="n">
         <v>0.04</v>
       </c>
       <c r="AD2" t="n">
-        <v>8.25</v>
+        <v>8.51</v>
       </c>
       <c r="AE2" t="n">
         <v>1774483200</v>
@@ -4141,29 +4141,29 @@
         <v>9.289999999999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.551</v>
+        <v>0.491</v>
       </c>
       <c r="AI2" t="n">
-        <v>159000</v>
+        <v>1362000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>159000</v>
+        <v>1362000</v>
       </c>
       <c r="AK2" t="n">
-        <v>531133</v>
+        <v>465169</v>
       </c>
       <c r="AL2" t="n">
-        <v>390900</v>
+        <v>214400</v>
       </c>
       <c r="AM2" t="n">
-        <v>390900</v>
+        <v>214400</v>
       </c>
       <c r="AN2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AO2" t="n">
         <v>0.48</v>
       </c>
-      <c r="AO2" t="n">
-        <v>0.485</v>
-      </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
@@ -4171,13 +4171,13 @@
         <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>468233568</v>
+        <v>453752096</v>
       </c>
       <c r="AS2" t="n">
-        <v>463406400</v>
+        <v>458579250</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
       <c r="AU2" t="n">
         <v>0.57</v>
@@ -4189,19 +4189,19 @@
         <v>0.335</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.2958336</v>
+        <v>0.2866841</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.4933</v>
+        <v>0.4897</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.512575</v>
+        <v>0.509275</v>
       </c>
       <c r="BA2" t="n">
         <v>0.02</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.041666668</v>
+        <v>0.04210526</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>144811552</v>
+        <v>130330096</v>
       </c>
       <c r="BF2" t="n">
         <v>-0.06131</v>
@@ -4236,7 +4236,7 @@
         <v>1.615</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.3003096</v>
+        <v>0.29102167</v>
       </c>
       <c r="BN2" t="n">
         <v>1751241600</v>
@@ -4254,16 +4254,16 @@
         <v>-0.1</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.091</v>
+        <v>0.082</v>
       </c>
       <c r="BT2" t="n">
-        <v>2.327</v>
+        <v>2.094</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.04000002</v>
+        <v>-0.06862748</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.02</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>0.485</v>
+        <v>0.47</v>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
@@ -4378,138 +4378,138 @@
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DC2" t="inlineStr">
+          <t>PRE</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>-1.0526305</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1323135000000</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.004999995</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>0.47 - 0.475</t>
+        </is>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>465169</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>0.47 - 0.57</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>-0.09999999399999999</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>-0.17543858</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-6.8627477</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1740369979</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1740369979</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.01969999</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>-0.040228695</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.03927502</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.07711947</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EA2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>SITOY GROUP</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>Sitoy Group Holdings Limited</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="EF2" t="inlineStr">
         <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DD2" t="inlineStr">
+      <c r="EG2" t="inlineStr">
         <is>
           <t>finmb_143104231</t>
         </is>
       </c>
-      <c r="DE2" t="inlineStr">
+      <c r="EH2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
+      <c r="EI2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DG2" t="n">
+      <c r="EJ2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="EK2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DI2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>1780382316</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1.0416719</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>Sitoy Group Holdings Limited</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.008299977</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.016825413</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.027574956</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>-0.053796925</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>15</v>
-      </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>SITOY GROUP</t>
-        </is>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>1323135000000</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.005000025</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>0.48 - 0.485</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EB2" t="n">
-        <v>531133</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>0.005000025</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0.010416719</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>0.48 - 0.57</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>-0.08499998</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>-0.14912277</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-4.000002</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>1740369979</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>1740369979</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-0.1</v>
+      <c r="EL2" t="b">
+        <v>0</v>
       </c>
       <c r="EM2" t="inlineStr"/>
     </row>
